--- a/eficiencia.xlsx
+++ b/eficiencia.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>N</t>
   </si>
@@ -53,13 +53,19 @@
     <t>1PB</t>
   </si>
   <si>
-    <t>Tiempo O(log n)</t>
+    <t>Tiempo seg O(log n)</t>
   </si>
   <si>
-    <t>T O(n)</t>
+    <t>T seg O(n)</t>
   </si>
   <si>
-    <t>T O(n^2)</t>
+    <t>T seg O(n^2)</t>
+  </si>
+  <si>
+    <t>T min O(n)</t>
+  </si>
+  <si>
+    <t>T años O(n^2)</t>
   </si>
 </sst>
 </file>
@@ -97,9 +103,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -380,7 +384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.90625" customWidth="1"/>
@@ -391,9 +395,11 @@
     <col min="7" max="7" width="12.6328125" customWidth="1"/>
     <col min="9" max="9" width="18.90625" customWidth="1"/>
     <col min="10" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -418,8 +424,14 @@
       <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B2">
         <f>2^C2</f>
         <v>2</v>
@@ -451,8 +463,16 @@
         <f>G2/(3.5*(10^12))</f>
         <v>1.1428571428571429E-12</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M2">
+        <f>J2/60</f>
+        <v>9.523809523809525E-15</v>
+      </c>
+      <c r="O2">
+        <f>K2/(60*60*24*365)</f>
+        <v>3.6239762267159529E-20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B3">
         <f>2^C3</f>
         <v>4</v>
@@ -484,10 +504,18 @@
         <f t="shared" ref="K3:K51" si="5">G3/(3.5*(10^12))</f>
         <v>4.5714285714285718E-12</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M3">
+        <f t="shared" ref="M3:M52" si="6">J3/60</f>
+        <v>1.904761904761905E-14</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O51" si="7">K3/(60*60*24*365)</f>
+        <v>1.4495904906863812E-19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4">
-        <f t="shared" ref="B4:B51" si="6">2^C4</f>
+        <f t="shared" ref="B4:B51" si="8">2^C4</f>
         <v>8</v>
       </c>
       <c r="C4">
@@ -517,10 +545,18 @@
         <f t="shared" si="5"/>
         <v>1.8285714285714287E-11</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M4">
+        <f t="shared" si="6"/>
+        <v>3.80952380952381E-14</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="7"/>
+        <v>5.7983619627455247E-19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="C5">
@@ -550,10 +586,18 @@
         <f t="shared" si="5"/>
         <v>7.3142857142857149E-11</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M5">
+        <f t="shared" si="6"/>
+        <v>7.61904761904762E-14</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="7"/>
+        <v>2.3193447850982099E-18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
       <c r="C6">
@@ -583,10 +627,18 @@
         <f t="shared" si="5"/>
         <v>2.925714285714286E-10</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M6">
+        <f t="shared" si="6"/>
+        <v>1.523809523809524E-13</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="7"/>
+        <v>9.2773791403928395E-18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>64</v>
       </c>
       <c r="C7">
@@ -616,10 +668,18 @@
         <f t="shared" si="5"/>
         <v>1.1702857142857144E-9</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M7">
+        <f t="shared" si="6"/>
+        <v>3.047619047619048E-13</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="7"/>
+        <v>3.7109516561571358E-17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>128</v>
       </c>
       <c r="C8">
@@ -649,10 +709,18 @@
         <f t="shared" si="5"/>
         <v>4.6811428571428575E-9</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M8">
+        <f t="shared" si="6"/>
+        <v>6.095238095238096E-13</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="7"/>
+        <v>1.4843806624628543E-16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>256</v>
       </c>
       <c r="C9">
@@ -682,10 +750,18 @@
         <f t="shared" si="5"/>
         <v>1.872457142857143E-8</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M9">
+        <f t="shared" si="6"/>
+        <v>1.2190476190476192E-12</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="7"/>
+        <v>5.9375226498514173E-16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>512</v>
       </c>
       <c r="C10">
@@ -715,13 +791,21 @@
         <f t="shared" si="5"/>
         <v>7.489828571428572E-8</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M10">
+        <f t="shared" si="6"/>
+        <v>2.4380952380952384E-12</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="7"/>
+        <v>2.3750090599405669E-15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>4</v>
       </c>
       <c r="B11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1024</v>
       </c>
       <c r="C11">
@@ -751,10 +835,18 @@
         <f t="shared" si="5"/>
         <v>2.9959314285714288E-7</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M11">
+        <f t="shared" si="6"/>
+        <v>4.8761904761904768E-12</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="7"/>
+        <v>9.5000362397622676E-15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2048</v>
       </c>
       <c r="C12">
@@ -784,10 +876,18 @@
         <f t="shared" si="5"/>
         <v>1.1983725714285715E-6</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M12">
+        <f t="shared" si="6"/>
+        <v>9.7523809523809536E-12</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="7"/>
+        <v>3.8000144959049071E-14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4096</v>
       </c>
       <c r="C13">
@@ -817,10 +917,18 @@
         <f t="shared" si="5"/>
         <v>4.7934902857142861E-6</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M13">
+        <f t="shared" si="6"/>
+        <v>1.9504761904761907E-11</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="7"/>
+        <v>1.5200057983619628E-13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8192</v>
       </c>
       <c r="C14">
@@ -850,10 +958,18 @@
         <f t="shared" si="5"/>
         <v>1.9173961142857144E-5</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M14">
+        <f t="shared" si="6"/>
+        <v>3.9009523809523814E-11</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="7"/>
+        <v>6.0800231934478513E-13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>16384</v>
       </c>
       <c r="C15">
@@ -883,10 +999,18 @@
         <f t="shared" si="5"/>
         <v>7.6695844571428578E-5</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M15">
+        <f t="shared" si="6"/>
+        <v>7.8019047619047629E-11</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="7"/>
+        <v>2.4320092773791405E-12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>32768</v>
       </c>
       <c r="C16">
@@ -916,10 +1040,18 @@
         <f t="shared" si="5"/>
         <v>3.0678337828571431E-4</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M16">
+        <f t="shared" si="6"/>
+        <v>1.5603809523809526E-10</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="7"/>
+        <v>9.7280371095165621E-12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>65536</v>
       </c>
       <c r="C17">
@@ -949,10 +1081,18 @@
         <f t="shared" si="5"/>
         <v>1.2271335131428572E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M17">
+        <f t="shared" si="6"/>
+        <v>3.1207619047619052E-10</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="7"/>
+        <v>3.8912148438066248E-11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>131072</v>
       </c>
       <c r="C18">
@@ -982,10 +1122,18 @@
         <f>G18/(3.5*(10^12))</f>
         <v>4.908534052571429E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M18">
+        <f t="shared" si="6"/>
+        <v>6.2415238095238103E-10</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="7"/>
+        <v>1.5564859375226499E-10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>262144</v>
       </c>
       <c r="C19">
@@ -1015,10 +1163,18 @@
         <f t="shared" si="5"/>
         <v>1.9634136210285716E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M19">
+        <f t="shared" si="6"/>
+        <v>1.2483047619047621E-9</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="7"/>
+        <v>6.2259437500905997E-10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B20">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>524288</v>
       </c>
       <c r="C20">
@@ -1048,13 +1204,21 @@
         <f t="shared" si="5"/>
         <v>7.8536544841142863E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M20">
+        <f>J20/60</f>
+        <v>2.4966095238095241E-9</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="7"/>
+        <v>2.4903775000362399E-9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>5</v>
       </c>
       <c r="B21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1048576</v>
       </c>
       <c r="C21">
@@ -1084,10 +1248,18 @@
         <f t="shared" si="5"/>
         <v>0.31414617936457145</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M21">
+        <f t="shared" si="6"/>
+        <v>4.9932190476190482E-9</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="7"/>
+        <v>9.9615100001449595E-9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2097152</v>
       </c>
       <c r="C22">
@@ -1117,8 +1289,16 @@
         <f t="shared" si="5"/>
         <v>1.2565847174582858</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M22">
+        <f t="shared" si="6"/>
+        <v>9.9864380952380965E-9</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="7"/>
+        <v>3.9846040000579838E-8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B23">
         <f>2^C23</f>
         <v>4194304</v>
@@ -1150,10 +1330,18 @@
         <f t="shared" si="5"/>
         <v>5.0263388698331433</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M23">
+        <f t="shared" si="6"/>
+        <v>1.9972876190476193E-8</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="7"/>
+        <v>1.5938416000231935E-7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B24">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8388608</v>
       </c>
       <c r="C24">
@@ -1183,8 +1371,16 @@
         <f t="shared" si="5"/>
         <v>20.105355479332573</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M24">
+        <f t="shared" si="6"/>
+        <v>3.9945752380952386E-8</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="7"/>
+        <v>6.3753664000927741E-7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B25">
         <f>2^C25</f>
         <v>16777216</v>
@@ -1216,10 +1412,18 @@
         <f t="shared" si="5"/>
         <v>80.421421917330292</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M25">
+        <f t="shared" si="6"/>
+        <v>7.9891504761904772E-8</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="7"/>
+        <v>2.5501465600371096E-6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B26">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>33554432</v>
       </c>
       <c r="C26">
@@ -1249,10 +1453,18 @@
         <f t="shared" si="5"/>
         <v>321.68568766932117</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M26">
+        <f t="shared" si="6"/>
+        <v>1.5978300952380954E-7</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="7"/>
+        <v>1.0200586240148439E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B27">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>67108864</v>
       </c>
       <c r="C27">
@@ -1282,10 +1494,18 @@
         <f t="shared" si="5"/>
         <v>1286.7427506772847</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M27">
+        <f t="shared" si="6"/>
+        <v>3.1956601904761909E-7</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="7"/>
+        <v>4.0802344960593754E-5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B28">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>134217728</v>
       </c>
       <c r="C28">
@@ -1315,10 +1535,18 @@
         <f t="shared" si="5"/>
         <v>5146.9710027091387</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M28">
+        <f t="shared" si="6"/>
+        <v>6.3913203809523818E-7</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="7"/>
+        <v>1.6320937984237502E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B29">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>268435456</v>
       </c>
       <c r="C29">
@@ -1348,10 +1576,18 @@
         <f t="shared" si="5"/>
         <v>20587.884010836555</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M29">
+        <f t="shared" si="6"/>
+        <v>1.2782640761904764E-6</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="7"/>
+        <v>6.5283751936950007E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>536870912</v>
       </c>
       <c r="C30">
@@ -1381,13 +1617,21 @@
         <f t="shared" si="5"/>
         <v>82351.536043346219</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M30">
+        <f t="shared" si="6"/>
+        <v>2.5565281523809527E-6</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="7"/>
+        <v>2.6113500774780003E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
       <c r="B31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1073741824</v>
       </c>
       <c r="C31">
@@ -1417,10 +1661,18 @@
         <f t="shared" si="5"/>
         <v>329406.14417338488</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M31">
+        <f t="shared" si="6"/>
+        <v>5.1130563047619054E-6</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="7"/>
+        <v>1.0445400309912001E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2147483648</v>
       </c>
       <c r="C32">
@@ -1450,10 +1702,18 @@
         <f>G32/(3.5*(10^12))</f>
         <v>1317624.5766935395</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M32">
+        <f t="shared" si="6"/>
+        <v>1.0226112609523811E-5</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="7"/>
+        <v>4.1781601239648004E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B33">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4294967296</v>
       </c>
       <c r="C33">
@@ -1483,10 +1743,18 @@
         <f t="shared" si="5"/>
         <v>5270498.306774158</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M33">
+        <f t="shared" si="6"/>
+        <v>2.0452225219047622E-5</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="7"/>
+        <v>0.16712640495859202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B34">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8589934592</v>
       </c>
       <c r="C34">
@@ -1516,10 +1784,18 @@
         <f t="shared" si="5"/>
         <v>21081993.227096632</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M34">
+        <f t="shared" si="6"/>
+        <v>4.0904450438095243E-5</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="7"/>
+        <v>0.66850561983436807</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>17179869184</v>
       </c>
       <c r="C35">
@@ -1549,10 +1825,18 @@
         <f>G35/(3.5*(10^12))</f>
         <v>84327972.908386528</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M35">
+        <f t="shared" si="6"/>
+        <v>8.1808900876190486E-5</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="7"/>
+        <v>2.6740224793374723</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B36">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>34359738368</v>
       </c>
       <c r="C36">
@@ -1582,10 +1866,18 @@
         <f t="shared" si="5"/>
         <v>337311891.63354611</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M36">
+        <f t="shared" si="6"/>
+        <v>1.6361780175238097E-4</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="7"/>
+        <v>10.696089917349889</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B37">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>68719476736</v>
       </c>
       <c r="C37">
@@ -1615,10 +1907,18 @@
         <f t="shared" si="5"/>
         <v>1349247566.5341845</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M37">
+        <f>J37/60</f>
+        <v>3.2723560350476195E-4</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="7"/>
+        <v>42.784359669399556</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B38">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>137438953472</v>
       </c>
       <c r="C38">
@@ -1648,10 +1948,18 @@
         <f t="shared" si="5"/>
         <v>5396990266.1367378</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M38">
+        <f t="shared" si="6"/>
+        <v>6.5447120700952389E-4</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="7"/>
+        <v>171.13743867759823</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B39">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>274877906944</v>
       </c>
       <c r="C39">
@@ -1681,10 +1989,18 @@
         <f t="shared" si="5"/>
         <v>21587961064.546951</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M39">
+        <f t="shared" si="6"/>
+        <v>1.3089424140190478E-3</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="7"/>
+        <v>684.5497547103929</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>549755813888</v>
       </c>
       <c r="C40">
@@ -1714,13 +2030,21 @@
         <f t="shared" si="5"/>
         <v>86351844258.187805</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M40">
+        <f t="shared" si="6"/>
+        <v>2.6178848280380956E-3</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="7"/>
+        <v>2738.1990188415716</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>6</v>
       </c>
       <c r="B41">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1099511627776</v>
       </c>
       <c r="C41">
@@ -1750,10 +2074,18 @@
         <f t="shared" si="5"/>
         <v>345407377032.75122</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M41">
+        <f t="shared" si="6"/>
+        <v>5.2357696560761911E-3</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="7"/>
+        <v>10952.796075366286</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B42">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>2199023255552</v>
       </c>
       <c r="C42">
@@ -1783,10 +2115,18 @@
         <f t="shared" si="5"/>
         <v>1381629508131.0049</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M42">
+        <f t="shared" si="6"/>
+        <v>1.0471539312152382E-2</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="7"/>
+        <v>43811.184301465146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B43">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>4398046511104</v>
       </c>
       <c r="C43">
@@ -1816,10 +2156,18 @@
         <f t="shared" si="5"/>
         <v>5526518032524.0195</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M43">
+        <f>J43/60</f>
+        <v>2.0943078624304765E-2</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="7"/>
+        <v>175244.73720586058</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>8796093022208</v>
       </c>
       <c r="C44">
@@ -1849,10 +2197,18 @@
         <f t="shared" si="5"/>
         <v>22106072130096.078</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M44">
+        <f t="shared" si="6"/>
+        <v>4.1886157248609529E-2</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="7"/>
+        <v>700978.94882344233</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>17592186044416</v>
       </c>
       <c r="C45">
@@ -1882,10 +2238,18 @@
         <f t="shared" si="5"/>
         <v>88424288520384.313</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M45">
+        <f t="shared" si="6"/>
+        <v>8.3772314497219058E-2</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="7"/>
+        <v>2803915.7952937693</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B46">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>35184372088832</v>
       </c>
       <c r="C46">
@@ -1915,10 +2279,18 @@
         <f t="shared" si="5"/>
         <v>353697154081537.25</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M46">
+        <f t="shared" si="6"/>
+        <v>0.16754462899443812</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="7"/>
+        <v>11215663.181175077</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B47">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>70368744177664</v>
       </c>
       <c r="C47">
@@ -1948,10 +2320,18 @@
         <f>G47/(3.5*(10^12))</f>
         <v>1414788616326149</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M47">
+        <f t="shared" si="6"/>
+        <v>0.33508925798887623</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="7"/>
+        <v>44862652.724700309</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B48">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>140737488355328</v>
       </c>
       <c r="C48">
@@ -1981,10 +2361,18 @@
         <f t="shared" si="5"/>
         <v>5659154465304596</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M48">
+        <f t="shared" si="6"/>
+        <v>0.67017851597775246</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="7"/>
+        <v>179450610.89880124</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B49">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>281474976710656</v>
       </c>
       <c r="C49">
@@ -2014,10 +2402,18 @@
         <f t="shared" si="5"/>
         <v>2.2636617861218384E+16</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M49">
+        <f t="shared" si="6"/>
+        <v>1.3403570319555049</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="7"/>
+        <v>717802443.59520495</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B50">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>562949953421312</v>
       </c>
       <c r="C50">
@@ -2047,13 +2443,21 @@
         <f t="shared" si="5"/>
         <v>9.0546471444873536E+16</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M50">
+        <f t="shared" si="6"/>
+        <v>2.6807140639110099</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="7"/>
+        <v>2871209774.3808198</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>8</v>
       </c>
       <c r="B51">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1125899906842624</v>
       </c>
       <c r="C51">
@@ -2082,6 +2486,14 @@
       <c r="K51">
         <f t="shared" si="5"/>
         <v>3.6218588577949414E+17</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="6"/>
+        <v>5.3614281278220197</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="7"/>
+        <v>11484839097.523279</v>
       </c>
     </row>
   </sheetData>
